--- a/data/trans_bre/P19C04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -3,62</t>
+          <t>-12,92; -3,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -10,3</t>
+          <t>-19,41; -10,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,87; -5,67</t>
+          <t>-17,17; -6,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -5,87</t>
+          <t>-14,93; -6,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,09; -12,76</t>
+          <t>-38,75; -13,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,54; -26,42</t>
+          <t>-43,68; -27,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,41; -18,98</t>
+          <t>-46,66; -19,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -19,21</t>
+          <t>-40,18; -20,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -3,73</t>
+          <t>-9,51; -3,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -4,3</t>
+          <t>-9,69; -4,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -2,32</t>
+          <t>-7,26; -2,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -0,12</t>
+          <t>-6,96; 0,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -22,7</t>
+          <t>-47,88; -22,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,74; -22,01</t>
+          <t>-43,81; -23,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,05; -15,74</t>
+          <t>-41,55; -15,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,49; -4,29</t>
+          <t>-51,09; -4,34</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,66</t>
+          <t>-5,53; 1,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 1,79</t>
+          <t>-6,92; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,73</t>
+          <t>-4,23; 2,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; -0,84</t>
+          <t>-6,02; -0,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 27,18</t>
+          <t>-55,17; 24,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 24,22</t>
+          <t>-54,43; 25,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 40,1</t>
+          <t>-41,11; 40,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,97; -12,5</t>
+          <t>-59,01; -5,5</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -3,19</t>
+          <t>-7,22; -3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -5,02</t>
+          <t>-9,62; -5,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,69; -2,69</t>
+          <t>-6,63; -2,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; -0,78</t>
+          <t>-6,31; -1,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,32; -17,24</t>
+          <t>-34,5; -17,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; -21,2</t>
+          <t>-36,45; -21,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,62; -15,77</t>
+          <t>-35,21; -15,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,86; -7,84</t>
+          <t>-40,64; -10,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C04-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,66</t>
+          <t>-11,31</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-31,28%</t>
+          <t>-32,84%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; -3,81</t>
+          <t>-12,53; -3,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -10,62</t>
+          <t>-19,62; -10,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -6,2</t>
+          <t>-16,78; -5,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,93; -6,43</t>
+          <t>-15,87; -6,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,75; -13,31</t>
+          <t>-37,71; -13,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,68; -27,35</t>
+          <t>-44,54; -27,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-46,66; -19,58</t>
+          <t>-46,1; -18,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,18; -20,4</t>
+          <t>-42,22; -22,51</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,05</t>
+          <t>-5,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-33,63%</t>
+          <t>-34,83%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -3,77</t>
+          <t>-9,33; -3,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -4,45</t>
+          <t>-9,79; -4,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,26; -2,47</t>
+          <t>-7,21; -2,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,03</t>
+          <t>-7,17; -3,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-47,88; -22,64</t>
+          <t>-47,47; -23,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,81; -23,07</t>
+          <t>-43,99; -22,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,55; -15,74</t>
+          <t>-41,77; -15,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,09; -4,34</t>
+          <t>-44,96; -23,8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>-3,4</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-40,24%</t>
+          <t>-41,47%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,55</t>
+          <t>-5,63; 1,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 1,92</t>
+          <t>-6,67; 1,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 2,69</t>
+          <t>-4,32; 2,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -0,56</t>
+          <t>-5,94; -0,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 24,38</t>
+          <t>-54,64; 28,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 25,32</t>
+          <t>-54,81; 21,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,11; 40,16</t>
+          <t>-42,17; 44,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,01; -5,5</t>
+          <t>-60,75; -13,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,94</t>
+          <t>-4,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-27,23%</t>
+          <t>-29,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -3,2</t>
+          <t>-7,41; -3,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; -5,23</t>
+          <t>-9,42; -5,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -2,53</t>
+          <t>-6,64; -2,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -1,06</t>
+          <t>-6,52; -3,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,5; -17,02</t>
+          <t>-34,97; -16,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,45; -21,84</t>
+          <t>-36,53; -21,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -15,22</t>
+          <t>-34,86; -15,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,64; -10,64</t>
+          <t>-37,26; -20,71</t>
         </is>
       </c>
     </row>
